--- a/word/csvfile/转换结果20260227.xlsx
+++ b/word/csvfile/转换结果20260227.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuanyuqing/Documents/code/schoolProject/word/csvfile/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FECD01E-EA37-2740-AD9D-9FE524886B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="105" windowWidth="19395" windowHeight="7605"/>
+    <workbookView xWindow="600" yWindow="760" windowWidth="28300" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="75">
   <si>
     <t>名称</t>
   </si>
@@ -218,114 +224,125 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>取值范围 0~400</t>
+  </si>
+  <si>
+    <t>0x000000477*x+0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>某设备装置测量数据4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>某设备装置测量数据5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x8003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x8004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>某设备装置测量数据6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>某状态信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>某状态信息2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信息1</t>
+  </si>
+  <si>
+    <t>消息1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置信息</t>
+  </si>
+  <si>
+    <t>信息2</t>
+  </si>
+  <si>
+    <t>综合状态数据</t>
+  </si>
+  <si>
+    <t>电流</t>
+  </si>
+  <si>
+    <t>信道状态</t>
+  </si>
+  <si>
+    <t>状态4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态2</t>
+  </si>
+  <si>
+    <t>状态1</t>
+  </si>
+  <si>
+    <t>UINT8</t>
+  </si>
+  <si>
+    <t>[0,4294967295]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,255]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,65535]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,400]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>某设备装置测量数据7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
     <t>惯性测量系 °/h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>°/h</t>
   </si>
   <si>
     <t>0 ~0xFFFF，实际电压/v = （模拟量采集数据/212）×21</t>
-  </si>
-  <si>
-    <t>取值范围 0~400</t>
-  </si>
-  <si>
-    <t>0x000000477*x+0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>某设备装置测量数据4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>某设备装置测量数据5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x8003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x8004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>状态信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>某设备装置测量数据6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>某状态信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>某状态信息2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>信息1</t>
-  </si>
-  <si>
-    <t>消息1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>位置信息</t>
-  </si>
-  <si>
-    <t>信息2</t>
-  </si>
-  <si>
-    <t>综合状态数据</t>
-  </si>
-  <si>
-    <t>电流</t>
-  </si>
-  <si>
-    <t>信道状态</t>
-  </si>
-  <si>
-    <t>状态4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>状态3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>状态2</t>
-  </si>
-  <si>
-    <t>状态1</t>
-  </si>
-  <si>
-    <t>UINT8</t>
-  </si>
-  <si>
-    <t>[0,4294967295]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0,255]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0,65535]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0,400]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>某设备装置测量数据7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8">
     <font>
       <sz val="11"/>
@@ -507,7 +524,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -523,13 +540,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
@@ -556,13 +567,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -580,13 +585,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -624,7 +637,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -658,6 +671,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -692,9 +706,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -867,9 +882,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q41"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
@@ -985,7 +1000,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="15">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -1011,17 +1026,17 @@
         <v>20</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="14.25">
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="15">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -1047,17 +1062,17 @@
         <v>20</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:17" s="7" customFormat="1" ht="14.25">
+    <row r="6" spans="1:17" ht="15">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
@@ -1079,9 +1094,9 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:17" s="7" customFormat="1" ht="14.25">
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:17" ht="15">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1099,13 +1114,13 @@
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:17" s="7" customFormat="1" ht="14.25">
+      <c r="P7" s="5"/>
+    </row>
+    <row r="8" spans="1:17" ht="15">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
@@ -1137,15 +1152,18 @@
         <v>20</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N8" s="1"/>
-      <c r="O8" s="1" t="s">
+      <c r="O8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:17" s="7" customFormat="1" ht="14.25">
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="1:17" ht="15">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1165,17 +1183,17 @@
         <v>20</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:17" ht="14.25">
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" ht="15">
       <c r="A10" s="3" t="s">
         <v>35</v>
       </c>
@@ -1207,13 +1225,16 @@
         <v>20</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N10" s="1"/>
-      <c r="O10" s="1" t="s">
+      <c r="O10" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P10" s="6"/>
+      <c r="Q10" s="5"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1"/>
@@ -1235,17 +1256,17 @@
         <v>20</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:17" ht="14.25">
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="1:17" ht="15">
       <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
@@ -1277,13 +1298,16 @@
         <v>20</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N12" s="1"/>
-      <c r="O12" s="1" t="s">
+      <c r="O12" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P12" s="6"/>
+      <c r="Q12" s="5"/>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="1"/>
@@ -1305,15 +1329,15 @@
         <v>20</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="1"/>
@@ -1335,13 +1359,16 @@
         <v>20</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N14" s="1"/>
-      <c r="O14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="P14" s="1"/>
+      <c r="O14" t="s">
+        <v>72</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1"/>
@@ -1363,15 +1390,18 @@
         <v>42</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P15" s="1"/>
+      <c r="O15" t="s">
+        <v>74</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="1"/>
@@ -1393,15 +1423,15 @@
         <v>42</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N16" s="1"/>
-      <c r="O16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="P16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1421,17 +1451,20 @@
         <v>20</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N17" s="1"/>
-      <c r="O17" s="1" t="s">
+      <c r="O17" t="s">
+        <v>22</v>
+      </c>
+      <c r="P17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" ht="14.25">
+      <c r="Q17" s="1"/>
+    </row>
+    <row r="18" spans="1:17" ht="15">
       <c r="A18" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1">
         <v>100</v>
@@ -1448,7 +1481,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>18</v>
@@ -1461,15 +1494,18 @@
         <v>20</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N18" s="1"/>
-      <c r="O18" s="1" t="s">
+      <c r="O18" t="s">
+        <v>70</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1489,19 +1525,19 @@
         <v>20</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" ht="14.25">
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20" spans="1:17" ht="15">
       <c r="A20" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1510,7 +1546,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>18</v>
@@ -1523,15 +1559,18 @@
         <v>20</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N20" s="1"/>
-      <c r="O20" s="1" t="s">
+      <c r="O20" t="s">
+        <v>70</v>
+      </c>
+      <c r="P20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1551,19 +1590,19 @@
         <v>20</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21" s="1"/>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1584,12 +1623,15 @@
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
-      <c r="O22" s="1" t="s">
+      <c r="O22" t="s">
+        <v>70</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22" s="1"/>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1612,14 +1654,14 @@
       <c r="N23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16" ht="14.25">
+      <c r="Q23" s="1"/>
+    </row>
+    <row r="24" spans="1:17" ht="15">
       <c r="A24" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1640,12 +1682,15 @@
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
-      <c r="O24" s="1" t="s">
+      <c r="O24" t="s">
+        <v>70</v>
+      </c>
+      <c r="P24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1668,14 +1713,14 @@
       <c r="N25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O25" s="1" t="s">
+      <c r="P25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" ht="14.25">
+      <c r="Q25" s="1"/>
+    </row>
+    <row r="26" spans="1:17" ht="15">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1696,12 +1741,15 @@
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
-      <c r="O26" s="1" t="s">
+      <c r="O26" t="s">
+        <v>70</v>
+      </c>
+      <c r="P26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P26" s="6"/>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26" s="5"/>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1724,14 +1772,14 @@
       <c r="N27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" ht="14.25">
+      <c r="Q27" s="1"/>
+    </row>
+    <row r="28" spans="1:17" ht="15">
       <c r="A28" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1751,15 +1799,18 @@
         <v>20</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N28" s="1"/>
-      <c r="O28" s="1" t="s">
+      <c r="O28" t="s">
+        <v>70</v>
+      </c>
+      <c r="P28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P28" s="6"/>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28" s="5"/>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1779,19 +1830,19 @@
         <v>20</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16" ht="14.25">
+      <c r="Q29" s="1"/>
+    </row>
+    <row r="30" spans="1:17" ht="15">
       <c r="A30" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1811,17 +1862,18 @@
         <v>20</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" s="1"/>
+      <c r="O30" t="s">
+        <v>70</v>
+      </c>
+      <c r="P30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P30" s="6"/>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="Q30" s="5"/>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1841,19 +1893,19 @@
         <v>20</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O31" s="1" t="s">
+      <c r="P31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="Q31" s="1"/>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1863,7 +1915,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1">
@@ -1887,7 +1939,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1">
@@ -1910,8 +1962,8 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="I34" s="10" t="s">
-        <v>57</v>
+      <c r="I34" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="1">
@@ -1925,9 +1977,9 @@
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
     </row>
-    <row r="35" spans="1:16">
-      <c r="A35" s="9" t="s">
-        <v>59</v>
+    <row r="35" spans="1:16" ht="15">
+      <c r="A35" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1935,13 +1987,13 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="12" t="s">
+      <c r="H35" s="6"/>
+      <c r="I35" s="10" t="s">
         <v>40</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="5" t="s">
+      <c r="L35" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M35" s="1"/>
@@ -1949,21 +2001,21 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
     </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="9"/>
+    <row r="36" spans="1:16" ht="15">
+      <c r="A36" s="7"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="J36" s="14"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="16" t="s">
+      <c r="H36" s="6"/>
+      <c r="I36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J36" s="12"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13" t="s">
         <v>27</v>
       </c>
       <c r="M36" s="1"/>
@@ -1971,26 +2023,26 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
     </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="9"/>
+    <row r="37" spans="1:16" ht="15">
+      <c r="A37" s="7"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="J37" s="19" t="b">
+      <c r="H37" s="6"/>
+      <c r="I37" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J37" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="K37" s="20">
+      <c r="K37" s="16">
         <v>8</v>
       </c>
-      <c r="L37" s="21" t="s">
-        <v>66</v>
+      <c r="L37" s="17" t="s">
+        <v>64</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="1"/>
@@ -1998,22 +2050,22 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="9"/>
+      <c r="A38" s="7"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="K38" s="11">
+      <c r="H38" s="6"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="K38" s="9">
         <v>1</v>
       </c>
-      <c r="L38" s="18" t="s">
+      <c r="L38" s="9" t="s">
         <v>27</v>
       </c>
       <c r="M38" s="1"/>
@@ -2022,7 +2074,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="9"/>
+      <c r="A39" s="7"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -2030,14 +2082,14 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="11"/>
+      <c r="I39" s="9"/>
       <c r="J39" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K39" s="1">
         <v>2</v>
       </c>
-      <c r="L39" s="5" t="s">
+      <c r="L39" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M39" s="1"/>
@@ -2046,7 +2098,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="9"/>
+      <c r="A40" s="7"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -2056,12 +2108,12 @@
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K40" s="1">
         <v>4</v>
       </c>
-      <c r="L40" s="5" t="s">
+      <c r="L40" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M40" s="1"/>
@@ -2070,7 +2122,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="9"/>
+      <c r="A41" s="7"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -2080,12 +2132,12 @@
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K41" s="1">
         <v>1</v>
       </c>
-      <c r="L41" s="5" t="s">
+      <c r="L41" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M41" s="1"/>
@@ -2101,9 +2153,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2111,9 +2163,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/word/csvfile/转换结果20260227.xlsx
+++ b/word/csvfile/转换结果20260227.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuanyuqing/Documents/code/schoolProject/word/csvfile/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FECD01E-EA37-2740-AD9D-9FE524886B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AADB8F-EE42-0747-BB6B-70C73BD3E653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="760" windowWidth="28300" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1940" yWindow="3760" windowWidth="28300" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="74">
   <si>
     <t>名称</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>判读公式</t>
-  </si>
-  <si>
-    <t>转换公式</t>
   </si>
   <si>
     <t>单位</t>
@@ -336,7 +333,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>v</t>
+    <t>转换公式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -885,8 +883,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" ht="75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -927,18 +928,18 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:17" ht="15" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" hidden="1">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="B2" s="1">
         <v>100</v>
@@ -955,26 +956,26 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1">
         <v>32</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:17" hidden="1">
+    <row r="3" spans="1:17">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -984,28 +985,28 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1">
         <v>32</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:17" s="1" customFormat="1" ht="15">
       <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -1017,31 +1018,31 @@
         <v>3</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K4" s="1">
         <v>32</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" s="1" customFormat="1" ht="15">
       <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1053,28 +1054,28 @@
         <v>3</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" s="1">
         <v>32</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" ht="15">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1084,7 +1085,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1106,7 +1107,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1114,7 +1115,7 @@
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -1122,7 +1123,7 @@
     </row>
     <row r="8" spans="1:17" ht="15">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1">
         <v>100</v>
@@ -1139,27 +1140,27 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
         <v>32</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q8" s="5"/>
     </row>
@@ -1173,29 +1174,29 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
         <v>32</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q9" s="5"/>
     </row>
     <row r="10" spans="1:17" ht="15">
       <c r="A10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1">
         <v>100</v>
@@ -1212,27 +1213,27 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
         <v>32</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q10" s="5"/>
     </row>
@@ -1246,29 +1247,29 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
         <v>32</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="15">
       <c r="A12" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1">
         <v>100</v>
@@ -1285,27 +1286,27 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
         <v>32</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q12" s="5"/>
     </row>
@@ -1319,23 +1320,23 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
         <v>32</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q13" s="1"/>
     </row>
@@ -1349,24 +1350,24 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
         <v>32</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q14" s="1"/>
     </row>
@@ -1380,26 +1381,26 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
         <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O15" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q15" s="1"/>
     </row>
@@ -1413,21 +1414,21 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
         <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N16" s="1"/>
       <c r="P16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q16" s="1"/>
     </row>
@@ -1441,30 +1442,30 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1">
         <v>32</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="1:17" ht="15">
       <c r="A18" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1">
         <v>100</v>
@@ -1481,27 +1482,27 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
         <v>32</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q18" s="5"/>
     </row>
@@ -1515,29 +1516,29 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1">
         <v>32</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="1:17" ht="15">
       <c r="A20" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1546,27 +1547,27 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1">
         <v>32</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N20" s="1"/>
       <c r="O20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q20" s="5"/>
     </row>
@@ -1580,29 +1581,29 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1">
         <v>32</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1612,22 +1613,22 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1">
         <v>32</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q22" s="1"/>
     </row>
@@ -1641,27 +1642,27 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1">
         <v>32</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q23" s="1"/>
     </row>
     <row r="24" spans="1:17" ht="15">
       <c r="A24" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1671,22 +1672,22 @@
       <c r="G24" s="1"/>
       <c r="H24" s="4"/>
       <c r="I24" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1">
         <v>32</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q24" s="5"/>
     </row>
@@ -1700,27 +1701,27 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1">
         <v>32</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q25" s="1"/>
     </row>
     <row r="26" spans="1:17" ht="15">
       <c r="A26" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1730,22 +1731,22 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1">
         <v>32</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q26" s="5"/>
     </row>
@@ -1759,27 +1760,27 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1">
         <v>32</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q27" s="1"/>
     </row>
     <row r="28" spans="1:17" ht="15">
       <c r="A28" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1789,24 +1790,24 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1">
         <v>32</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N28" s="1"/>
       <c r="O28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q28" s="5"/>
     </row>
@@ -1820,29 +1821,29 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1">
         <v>32</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q29" s="1"/>
     </row>
     <row r="30" spans="1:17" ht="15">
       <c r="A30" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1852,24 +1853,24 @@
       <c r="G30" s="1"/>
       <c r="H30" s="4"/>
       <c r="I30" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1">
         <v>32</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N30" s="1"/>
       <c r="O30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q30" s="5"/>
     </row>
@@ -1883,29 +1884,29 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1">
         <v>32</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q31" s="1"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1915,14 +1916,14 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1">
         <v>16</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -1939,14 +1940,14 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1">
         <v>32</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -1963,14 +1964,14 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="1">
         <v>32</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -1979,7 +1980,7 @@
     </row>
     <row r="35" spans="1:16" ht="15">
       <c r="A35" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1989,12 +1990,12 @@
       <c r="G35" s="1"/>
       <c r="H35" s="6"/>
       <c r="I35" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -2011,12 +2012,12 @@
       <c r="G36" s="1"/>
       <c r="H36" s="6"/>
       <c r="I36" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J36" s="12"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
@@ -2033,7 +2034,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="6"/>
       <c r="I37" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J37" s="15" t="b">
         <v>0</v>
@@ -2042,7 +2043,7 @@
         <v>8</v>
       </c>
       <c r="L37" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="1"/>
@@ -2060,13 +2061,13 @@
       <c r="H38" s="6"/>
       <c r="I38" s="10"/>
       <c r="J38" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K38" s="9">
         <v>1</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
@@ -2084,13 +2085,13 @@
       <c r="H39" s="1"/>
       <c r="I39" s="9"/>
       <c r="J39" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K39" s="1">
         <v>2</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
@@ -2108,13 +2109,13 @@
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K40" s="1">
         <v>4</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
@@ -2132,13 +2133,13 @@
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K41" s="1">
         <v>1</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
